--- a/testAffichageML/ig/StructureDefinition-fr-lm-supporting-information.xlsx
+++ b/testAffichageML/ig/StructureDefinition-fr-lm-supporting-information.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="137">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T09:34:46+00:00</t>
+    <t>2026-05-18T13:21:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -354,10 +354,6 @@
   </si>
   <si>
     <t>fr-lm-supporting-information.subSection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-section
-</t>
   </si>
   <si>
     <t>Sous-sections</t>
@@ -1820,13 +1816,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L11" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="M11" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1877,7 +1873,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1894,10 +1890,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1923,10 +1919,10 @@
         <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1977,7 +1973,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -1994,10 +1990,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2020,13 +2016,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="L13" t="s" s="2">
-        <v>119</v>
-      </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2077,7 +2073,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2094,10 +2090,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2120,13 +2116,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2177,7 +2173,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -2194,10 +2190,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2220,13 +2216,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2277,7 +2273,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -2294,10 +2290,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2320,13 +2316,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2377,7 +2373,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -2394,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2420,13 +2416,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="L17" t="s" s="2">
-        <v>126</v>
-      </c>
       <c r="M17" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2477,7 +2473,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2494,10 +2490,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2520,13 +2516,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L18" t="s" s="2">
-        <v>129</v>
-      </c>
       <c r="M18" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2577,7 +2573,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2594,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2620,13 +2616,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>132</v>
-      </c>
       <c r="M19" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2677,7 +2673,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2694,10 +2690,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2720,13 +2716,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="M20" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2777,7 +2773,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2794,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2823,10 +2819,10 @@
         <v>80</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2877,7 +2873,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
